--- a/Proyecto Interno/composicion-nut/1823_mapeo_sipsa_tcac v1.0_2025.xlsx
+++ b/Proyecto Interno/composicion-nut/1823_mapeo_sipsa_tcac v1.0_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/composicion-nut/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{B138571D-3664-4E25-BFF5-D05DDD42E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2E47404-59FE-4A20-9BDF-DB80F2363D76}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{B138571D-3664-4E25-BFF5-D05DDD42E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF32366-7C4C-4FAA-8DE6-7400D452FE39}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2977,6 +2977,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3266,6 +3270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF10B127-6165-4A57-AAED-596F28B83BE3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AN368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3392,7 +3397,7 @@
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
     </row>
-    <row r="2" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -3499,7 +3504,7 @@
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
     </row>
-    <row r="3" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
@@ -3606,7 +3611,7 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
     </row>
-    <row r="4" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3713,7 +3718,7 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
     </row>
-    <row r="5" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -3820,7 +3825,7 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
     </row>
-    <row r="6" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -3927,7 +3932,7 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
     </row>
-    <row r="7" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -4038,7 +4043,7 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
     </row>
-    <row r="8" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
@@ -4147,7 +4152,7 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
     </row>
-    <row r="9" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4256,7 +4261,7 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
     </row>
-    <row r="10" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -4365,7 +4370,7 @@
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
     </row>
-    <row r="11" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -4474,7 +4479,7 @@
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
     </row>
-    <row r="12" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>57</v>
       </c>
@@ -4585,7 +4590,7 @@
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
     </row>
-    <row r="13" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -4694,7 +4699,7 @@
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
     </row>
-    <row r="14" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -4803,7 +4808,7 @@
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
     </row>
-    <row r="15" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -4912,7 +4917,7 @@
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
     </row>
-    <row r="16" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>65</v>
       </c>
@@ -5021,7 +5026,7 @@
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
     </row>
-    <row r="17" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
@@ -5128,7 +5133,7 @@
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
     </row>
-    <row r="18" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -5235,7 +5240,7 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
     </row>
-    <row r="19" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>70</v>
       </c>
@@ -5344,7 +5349,7 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
     </row>
-    <row r="20" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
@@ -5453,7 +5458,7 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
     </row>
-    <row r="21" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
@@ -5564,7 +5569,7 @@
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
     </row>
-    <row r="22" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>76</v>
       </c>
@@ -5675,7 +5680,7 @@
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
     </row>
-    <row r="23" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>79</v>
       </c>
@@ -5784,7 +5789,7 @@
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
     </row>
-    <row r="24" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>80</v>
       </c>
@@ -5895,7 +5900,7 @@
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
     </row>
-    <row r="25" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>81</v>
       </c>
@@ -6006,7 +6011,7 @@
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
     </row>
-    <row r="26" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -6117,7 +6122,7 @@
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
     </row>
-    <row r="27" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>84</v>
       </c>
@@ -6228,7 +6233,7 @@
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
     </row>
-    <row r="28" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -6329,7 +6334,7 @@
       <c r="AL28" s="1"/>
       <c r="AM28" s="1"/>
     </row>
-    <row r="29" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
@@ -6438,7 +6443,7 @@
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
     </row>
-    <row r="30" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -6547,7 +6552,7 @@
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
     </row>
-    <row r="31" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>92</v>
       </c>
@@ -6656,7 +6661,7 @@
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
     </row>
-    <row r="32" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>94</v>
       </c>
@@ -6765,7 +6770,7 @@
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
     </row>
-    <row r="33" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>96</v>
       </c>
@@ -6872,7 +6877,7 @@
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
     </row>
-    <row r="34" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>98</v>
       </c>
@@ -6979,7 +6984,7 @@
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
     </row>
-    <row r="35" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>100</v>
       </c>
@@ -7086,7 +7091,7 @@
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
     </row>
-    <row r="36" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>102</v>
       </c>
@@ -7193,7 +7198,7 @@
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
     </row>
-    <row r="37" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>103</v>
       </c>
@@ -7304,7 +7309,7 @@
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
     </row>
-    <row r="38" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>105</v>
       </c>
@@ -7413,7 +7418,7 @@
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
     </row>
-    <row r="39" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>108</v>
       </c>
@@ -7522,7 +7527,7 @@
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
     </row>
-    <row r="40" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>109</v>
       </c>
@@ -7631,7 +7636,7 @@
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
     </row>
-    <row r="41" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>110</v>
       </c>
@@ -7742,7 +7747,7 @@
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
     </row>
-    <row r="42" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>112</v>
       </c>
@@ -7851,7 +7856,7 @@
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
     </row>
-    <row r="43" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
@@ -7960,7 +7965,7 @@
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
     </row>
-    <row r="44" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>115</v>
       </c>
@@ -8069,7 +8074,7 @@
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
     </row>
-    <row r="45" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>117</v>
       </c>
@@ -8178,7 +8183,7 @@
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
     </row>
-    <row r="46" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>119</v>
       </c>
@@ -8287,7 +8292,7 @@
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
     </row>
-    <row r="47" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>121</v>
       </c>
@@ -8396,7 +8401,7 @@
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
     </row>
-    <row r="48" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>123</v>
       </c>
@@ -8507,7 +8512,7 @@
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
     </row>
-    <row r="49" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
@@ -8618,7 +8623,7 @@
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
     </row>
-    <row r="50" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>126</v>
       </c>
@@ -8727,7 +8732,7 @@
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
     </row>
-    <row r="51" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>128</v>
       </c>
@@ -8838,7 +8843,7 @@
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
     </row>
-    <row r="52" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>130</v>
       </c>
@@ -8947,7 +8952,7 @@
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
     </row>
-    <row r="53" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>132</v>
       </c>
@@ -9056,7 +9061,7 @@
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
     </row>
-    <row r="54" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>134</v>
       </c>
@@ -9165,7 +9170,7 @@
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
     </row>
-    <row r="55" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>136</v>
       </c>
@@ -9272,7 +9277,7 @@
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
     </row>
-    <row r="56" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>138</v>
       </c>
@@ -9379,7 +9384,7 @@
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
     </row>
-    <row r="57" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>140</v>
       </c>
@@ -9480,7 +9485,7 @@
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
     </row>
-    <row r="58" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>143</v>
       </c>
@@ -9589,7 +9594,7 @@
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
     </row>
-    <row r="59" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>145</v>
       </c>
@@ -9696,7 +9701,7 @@
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
     </row>
-    <row r="60" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>147</v>
       </c>
@@ -9803,7 +9808,7 @@
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
     </row>
-    <row r="61" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>148</v>
       </c>
@@ -9912,7 +9917,7 @@
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
     </row>
-    <row r="62" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>150</v>
       </c>
@@ -10019,7 +10024,7 @@
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
     </row>
-    <row r="63" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>152</v>
       </c>
@@ -10128,7 +10133,7 @@
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
     </row>
-    <row r="64" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>154</v>
       </c>
@@ -10239,7 +10244,7 @@
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
     </row>
-    <row r="65" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>156</v>
       </c>
@@ -10340,7 +10345,7 @@
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
     </row>
-    <row r="66" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>160</v>
       </c>
@@ -10449,7 +10454,7 @@
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
     </row>
-    <row r="67" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>163</v>
       </c>
@@ -10558,7 +10563,7 @@
       <c r="AL67" s="1"/>
       <c r="AM67" s="1"/>
     </row>
-    <row r="68" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>164</v>
       </c>
@@ -10667,7 +10672,7 @@
       <c r="AL68" s="1"/>
       <c r="AM68" s="1"/>
     </row>
-    <row r="69" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>167</v>
       </c>
@@ -10776,7 +10781,7 @@
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
     </row>
-    <row r="70" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>169</v>
       </c>
@@ -10885,7 +10890,7 @@
       <c r="AL70" s="1"/>
       <c r="AM70" s="1"/>
     </row>
-    <row r="71" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>170</v>
       </c>
@@ -10994,7 +10999,7 @@
       <c r="AL71" s="1"/>
       <c r="AM71" s="1"/>
     </row>
-    <row r="72" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>173</v>
       </c>
@@ -11103,7 +11108,7 @@
       <c r="AL72" s="1"/>
       <c r="AM72" s="1"/>
     </row>
-    <row r="73" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>174</v>
       </c>
@@ -11212,7 +11217,7 @@
       <c r="AL73" s="1"/>
       <c r="AM73" s="1"/>
     </row>
-    <row r="74" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>177</v>
       </c>
@@ -11321,7 +11326,7 @@
       <c r="AL74" s="1"/>
       <c r="AM74" s="1"/>
     </row>
-    <row r="75" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>178</v>
       </c>
@@ -11430,7 +11435,7 @@
       <c r="AL75" s="1"/>
       <c r="AM75" s="1"/>
     </row>
-    <row r="76" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>180</v>
       </c>
@@ -11541,7 +11546,7 @@
       <c r="AL76" s="1"/>
       <c r="AM76" s="1"/>
     </row>
-    <row r="77" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
@@ -11650,7 +11655,7 @@
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
     </row>
-    <row r="78" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>185</v>
       </c>
@@ -11759,7 +11764,7 @@
       <c r="AL78" s="1"/>
       <c r="AM78" s="1"/>
     </row>
-    <row r="79" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
@@ -11868,7 +11873,7 @@
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
     </row>
-    <row r="80" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>188</v>
       </c>
@@ -11977,7 +11982,7 @@
       <c r="AL80" s="1"/>
       <c r="AM80" s="1"/>
     </row>
-    <row r="81" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>189</v>
       </c>
@@ -12086,7 +12091,7 @@
       <c r="AL81" s="1"/>
       <c r="AM81" s="1"/>
     </row>
-    <row r="82" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>190</v>
       </c>
@@ -12193,7 +12198,7 @@
       <c r="AL82" s="1"/>
       <c r="AM82" s="1"/>
     </row>
-    <row r="83" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>192</v>
       </c>
@@ -12302,7 +12307,7 @@
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
     </row>
-    <row r="84" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>193</v>
       </c>
@@ -12409,7 +12414,7 @@
       <c r="AL84" s="1"/>
       <c r="AM84" s="1"/>
     </row>
-    <row r="85" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>195</v>
       </c>
@@ -12512,7 +12517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>199</v>
       </c>
@@ -12621,7 +12626,7 @@
       <c r="AL86" s="1"/>
       <c r="AM86" s="1"/>
     </row>
-    <row r="87" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>201</v>
       </c>
@@ -12728,7 +12733,7 @@
       <c r="AL87" s="1"/>
       <c r="AM87" s="1"/>
     </row>
-    <row r="88" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>202</v>
       </c>
@@ -12837,7 +12842,7 @@
       <c r="AL88" s="1"/>
       <c r="AM88" s="1"/>
     </row>
-    <row r="89" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>204</v>
       </c>
@@ -12946,7 +12951,7 @@
       <c r="AL89" s="1"/>
       <c r="AM89" s="1"/>
     </row>
-    <row r="90" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>205</v>
       </c>
@@ -13053,7 +13058,7 @@
       <c r="AL90" s="1"/>
       <c r="AM90" s="1"/>
     </row>
-    <row r="91" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>207</v>
       </c>
@@ -13162,7 +13167,7 @@
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
     </row>
-    <row r="92" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>208</v>
       </c>
@@ -13271,7 +13276,7 @@
       <c r="AL92" s="1"/>
       <c r="AM92" s="1"/>
     </row>
-    <row r="93" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>209</v>
       </c>
@@ -13380,7 +13385,7 @@
       <c r="AL93" s="1"/>
       <c r="AM93" s="1"/>
     </row>
-    <row r="94" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>210</v>
       </c>
@@ -13487,7 +13492,7 @@
       <c r="AL94" s="1"/>
       <c r="AM94" s="1"/>
     </row>
-    <row r="95" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>211</v>
       </c>
@@ -13594,7 +13599,7 @@
       <c r="AL95" s="1"/>
       <c r="AM95" s="1"/>
     </row>
-    <row r="96" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>212</v>
       </c>
@@ -13701,7 +13706,7 @@
       <c r="AL96" s="1"/>
       <c r="AM96" s="1"/>
     </row>
-    <row r="97" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>213</v>
       </c>
@@ -13802,7 +13807,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="98" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>216</v>
       </c>
@@ -13911,7 +13916,7 @@
       <c r="AL98" s="1"/>
       <c r="AM98" s="1"/>
     </row>
-    <row r="99" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>218</v>
       </c>
@@ -14020,7 +14025,7 @@
       <c r="AL99" s="1"/>
       <c r="AM99" s="1"/>
     </row>
-    <row r="100" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>219</v>
       </c>
@@ -14129,7 +14134,7 @@
       <c r="AL100" s="1"/>
       <c r="AM100" s="1"/>
     </row>
-    <row r="101" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>220</v>
       </c>
@@ -14238,7 +14243,7 @@
       <c r="AL101" s="1"/>
       <c r="AM101" s="1"/>
     </row>
-    <row r="102" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>221</v>
       </c>
@@ -14337,7 +14342,7 @@
       <c r="AL102" s="1"/>
       <c r="AM102" s="1"/>
     </row>
-    <row r="103" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>225</v>
       </c>
@@ -14446,7 +14451,7 @@
       <c r="AL103" s="1"/>
       <c r="AM103" s="1"/>
     </row>
-    <row r="104" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>226</v>
       </c>
@@ -14545,7 +14550,7 @@
       <c r="AL104" s="1"/>
       <c r="AM104" s="1"/>
     </row>
-    <row r="105" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>227</v>
       </c>
@@ -14644,7 +14649,7 @@
       <c r="AL105" s="1"/>
       <c r="AM105" s="1"/>
     </row>
-    <row r="106" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>228</v>
       </c>
@@ -14755,7 +14760,7 @@
       <c r="AL106" s="1"/>
       <c r="AM106" s="1"/>
     </row>
-    <row r="107" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>231</v>
       </c>
@@ -14864,7 +14869,7 @@
       <c r="AL107" s="1"/>
       <c r="AM107" s="1"/>
     </row>
-    <row r="108" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>232</v>
       </c>
@@ -14975,7 +14980,7 @@
       <c r="AL108" s="1"/>
       <c r="AM108" s="1"/>
     </row>
-    <row r="109" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>233</v>
       </c>
@@ -15086,7 +15091,7 @@
       <c r="AL109" s="1"/>
       <c r="AM109" s="1"/>
     </row>
-    <row r="110" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>234</v>
       </c>
@@ -15195,7 +15200,7 @@
       <c r="AL110" s="1"/>
       <c r="AM110" s="1"/>
     </row>
-    <row r="111" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>235</v>
       </c>
@@ -15304,7 +15309,7 @@
       <c r="AL111" s="1"/>
       <c r="AM111" s="1"/>
     </row>
-    <row r="112" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>237</v>
       </c>
@@ -15403,7 +15408,7 @@
       <c r="AL112" s="1"/>
       <c r="AM112" s="1"/>
     </row>
-    <row r="113" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>240</v>
       </c>
@@ -15510,7 +15515,7 @@
       <c r="AL113" s="1"/>
       <c r="AM113" s="1"/>
     </row>
-    <row r="114" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>242</v>
       </c>
@@ -15621,7 +15626,7 @@
       <c r="AL114" s="1"/>
       <c r="AM114" s="1"/>
     </row>
-    <row r="115" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>245</v>
       </c>
@@ -15720,7 +15725,7 @@
       <c r="AL115" s="1"/>
       <c r="AM115" s="1"/>
     </row>
-    <row r="116" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>248</v>
       </c>
@@ -15829,7 +15834,7 @@
       <c r="AL116" s="1"/>
       <c r="AM116" s="1"/>
     </row>
-    <row r="117" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>250</v>
       </c>
@@ -15938,7 +15943,7 @@
       <c r="AL117" s="1"/>
       <c r="AM117" s="1"/>
     </row>
-    <row r="118" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>252</v>
       </c>
@@ -16049,7 +16054,7 @@
       <c r="AL118" s="1"/>
       <c r="AM118" s="1"/>
     </row>
-    <row r="119" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>255</v>
       </c>
@@ -16158,7 +16163,7 @@
       <c r="AL119" s="1"/>
       <c r="AM119" s="1"/>
     </row>
-    <row r="120" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>256</v>
       </c>
@@ -16267,7 +16272,7 @@
       <c r="AL120" s="1"/>
       <c r="AM120" s="1"/>
     </row>
-    <row r="121" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>258</v>
       </c>
@@ -16380,7 +16385,7 @@
       <c r="AL121" s="1"/>
       <c r="AM121" s="1"/>
     </row>
-    <row r="122" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>261</v>
       </c>
@@ -16489,7 +16494,7 @@
       <c r="AL122" s="1"/>
       <c r="AM122" s="1"/>
     </row>
-    <row r="123" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>263</v>
       </c>
@@ -16598,7 +16603,7 @@
       <c r="AL123" s="1"/>
       <c r="AM123" s="1"/>
     </row>
-    <row r="124" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>265</v>
       </c>
@@ -16707,7 +16712,7 @@
       <c r="AL124" s="1"/>
       <c r="AM124" s="1"/>
     </row>
-    <row r="125" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>267</v>
       </c>
@@ -16816,7 +16821,7 @@
       <c r="AL125" s="1"/>
       <c r="AM125" s="1"/>
     </row>
-    <row r="126" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>269</v>
       </c>
@@ -16927,7 +16932,7 @@
       <c r="AL126" s="1"/>
       <c r="AM126" s="1"/>
     </row>
-    <row r="127" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>271</v>
       </c>
@@ -17038,7 +17043,7 @@
       <c r="AL127" s="1"/>
       <c r="AM127" s="1"/>
     </row>
-    <row r="128" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>273</v>
       </c>
@@ -17147,7 +17152,7 @@
       <c r="AL128" s="1"/>
       <c r="AM128" s="1"/>
     </row>
-    <row r="129" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>274</v>
       </c>
@@ -17256,7 +17261,7 @@
       <c r="AL129" s="1"/>
       <c r="AM129" s="1"/>
     </row>
-    <row r="130" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>276</v>
       </c>
@@ -17355,7 +17360,7 @@
       <c r="AL130" s="1"/>
       <c r="AM130" s="1"/>
     </row>
-    <row r="131" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>278</v>
       </c>
@@ -17464,7 +17469,7 @@
       <c r="AL131" s="1"/>
       <c r="AM131" s="1"/>
     </row>
-    <row r="132" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>280</v>
       </c>
@@ -17573,7 +17578,7 @@
       <c r="AL132" s="1"/>
       <c r="AM132" s="1"/>
     </row>
-    <row r="133" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>282</v>
       </c>
@@ -17682,7 +17687,7 @@
       <c r="AL133" s="1"/>
       <c r="AM133" s="1"/>
     </row>
-    <row r="134" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>284</v>
       </c>
@@ -17791,7 +17796,7 @@
       <c r="AL134" s="1"/>
       <c r="AM134" s="1"/>
     </row>
-    <row r="135" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>286</v>
       </c>
@@ -17900,7 +17905,7 @@
       <c r="AL135" s="1"/>
       <c r="AM135" s="1"/>
     </row>
-    <row r="136" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>287</v>
       </c>
@@ -18011,7 +18016,7 @@
       <c r="AL136" s="1"/>
       <c r="AM136" s="1"/>
     </row>
-    <row r="137" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>289</v>
       </c>
@@ -18120,7 +18125,7 @@
       <c r="AL137" s="1"/>
       <c r="AM137" s="1"/>
     </row>
-    <row r="138" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>290</v>
       </c>
@@ -18229,7 +18234,7 @@
       <c r="AL138" s="1"/>
       <c r="AM138" s="1"/>
     </row>
-    <row r="139" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>292</v>
       </c>
@@ -18328,7 +18333,7 @@
       <c r="AL139" s="1"/>
       <c r="AM139" s="1"/>
     </row>
-    <row r="140" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>295</v>
       </c>
@@ -18437,7 +18442,7 @@
       <c r="AL140" s="1"/>
       <c r="AM140" s="1"/>
     </row>
-    <row r="141" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>296</v>
       </c>
@@ -18536,7 +18541,7 @@
       <c r="AL141" s="1"/>
       <c r="AM141" s="1"/>
     </row>
-    <row r="142" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>299</v>
       </c>
@@ -18645,7 +18650,7 @@
       <c r="AL142" s="1"/>
       <c r="AM142" s="1"/>
     </row>
-    <row r="143" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>301</v>
       </c>
@@ -18756,7 +18761,7 @@
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
     </row>
-    <row r="144" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>304</v>
       </c>
@@ -18865,7 +18870,7 @@
       <c r="AL144" s="1"/>
       <c r="AM144" s="1"/>
     </row>
-    <row r="145" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>306</v>
       </c>
@@ -18974,7 +18979,7 @@
       <c r="AL145" s="1"/>
       <c r="AM145" s="1"/>
     </row>
-    <row r="146" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>307</v>
       </c>
@@ -19085,7 +19090,7 @@
       <c r="AL146" s="1"/>
       <c r="AM146" s="1"/>
     </row>
-    <row r="147" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>309</v>
       </c>
@@ -19184,7 +19189,7 @@
       <c r="AL147" s="1"/>
       <c r="AM147" s="1"/>
     </row>
-    <row r="148" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>310</v>
       </c>
@@ -19291,7 +19296,7 @@
       <c r="AL148" s="1"/>
       <c r="AM148" s="1"/>
     </row>
-    <row r="149" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>312</v>
       </c>
@@ -19398,7 +19403,7 @@
       <c r="AL149" s="1"/>
       <c r="AM149" s="1"/>
     </row>
-    <row r="150" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>314</v>
       </c>
@@ -19509,7 +19514,7 @@
       <c r="AL150" s="1"/>
       <c r="AM150" s="1"/>
     </row>
-    <row r="151" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>317</v>
       </c>
@@ -19616,7 +19621,7 @@
       <c r="AL151" s="1"/>
       <c r="AM151" s="1"/>
     </row>
-    <row r="152" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>319</v>
       </c>
@@ -19725,7 +19730,7 @@
       <c r="AL152" s="1"/>
       <c r="AM152" s="1"/>
     </row>
-    <row r="153" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>321</v>
       </c>
@@ -19834,7 +19839,7 @@
       <c r="AL153" s="1"/>
       <c r="AM153" s="1"/>
     </row>
-    <row r="154" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>323</v>
       </c>
@@ -19933,7 +19938,7 @@
       <c r="AL154" s="1"/>
       <c r="AM154" s="1"/>
     </row>
-    <row r="155" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>326</v>
       </c>
@@ -20042,7 +20047,7 @@
       <c r="AL155" s="1"/>
       <c r="AM155" s="1"/>
     </row>
-    <row r="156" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>328</v>
       </c>
@@ -20151,7 +20156,7 @@
       <c r="AL156" s="1"/>
       <c r="AM156" s="1"/>
     </row>
-    <row r="157" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>330</v>
       </c>
@@ -20260,7 +20265,7 @@
       <c r="AL157" s="1"/>
       <c r="AM157" s="1"/>
     </row>
-    <row r="158" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>331</v>
       </c>
@@ -20369,7 +20374,7 @@
       <c r="AL158" s="1"/>
       <c r="AM158" s="1"/>
     </row>
-    <row r="159" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>332</v>
       </c>
@@ -20478,7 +20483,7 @@
       <c r="AL159" s="1"/>
       <c r="AM159" s="1"/>
     </row>
-    <row r="160" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>333</v>
       </c>
@@ -20587,7 +20592,7 @@
       <c r="AL160" s="1"/>
       <c r="AM160" s="1"/>
     </row>
-    <row r="161" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>335</v>
       </c>
@@ -20696,7 +20701,7 @@
       <c r="AL161" s="1"/>
       <c r="AM161" s="1"/>
     </row>
-    <row r="162" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>337</v>
       </c>
@@ -20805,7 +20810,7 @@
       <c r="AL162" s="1"/>
       <c r="AM162" s="1"/>
     </row>
-    <row r="163" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>339</v>
       </c>
@@ -20916,7 +20921,7 @@
       <c r="AL163" s="1"/>
       <c r="AM163" s="1"/>
     </row>
-    <row r="164" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>341</v>
       </c>
@@ -21023,7 +21028,7 @@
       <c r="AL164" s="1"/>
       <c r="AM164" s="1"/>
     </row>
-    <row r="165" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>343</v>
       </c>
@@ -21130,7 +21135,7 @@
       <c r="AL165" s="1"/>
       <c r="AM165" s="1"/>
     </row>
-    <row r="166" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>345</v>
       </c>
@@ -21239,7 +21244,7 @@
       <c r="AL166" s="1"/>
       <c r="AM166" s="1"/>
     </row>
-    <row r="167" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>347</v>
       </c>
@@ -21348,7 +21353,7 @@
       <c r="AL167" s="1"/>
       <c r="AM167" s="1"/>
     </row>
-    <row r="168" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>349</v>
       </c>
@@ -21457,7 +21462,7 @@
       <c r="AL168" s="1"/>
       <c r="AM168" s="1"/>
     </row>
-    <row r="169" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>350</v>
       </c>
@@ -21566,7 +21571,7 @@
       <c r="AL169" s="1"/>
       <c r="AM169" s="1"/>
     </row>
-    <row r="170" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>351</v>
       </c>
@@ -21675,7 +21680,7 @@
       <c r="AL170" s="1"/>
       <c r="AM170" s="1"/>
     </row>
-    <row r="171" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>352</v>
       </c>
@@ -21784,7 +21789,7 @@
       <c r="AL171" s="1"/>
       <c r="AM171" s="1"/>
     </row>
-    <row r="172" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>353</v>
       </c>
@@ -21893,7 +21898,7 @@
       <c r="AL172" s="1"/>
       <c r="AM172" s="1"/>
     </row>
-    <row r="173" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>354</v>
       </c>
@@ -22002,7 +22007,7 @@
       <c r="AL173" s="1"/>
       <c r="AM173" s="1"/>
     </row>
-    <row r="174" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>355</v>
       </c>
@@ -22111,7 +22116,7 @@
       <c r="AL174" s="1"/>
       <c r="AM174" s="1"/>
     </row>
-    <row r="175" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>356</v>
       </c>
@@ -22218,7 +22223,7 @@
       <c r="AL175" s="1"/>
       <c r="AM175" s="1"/>
     </row>
-    <row r="176" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>357</v>
       </c>
@@ -22327,7 +22332,7 @@
       <c r="AL176" s="1"/>
       <c r="AM176" s="1"/>
     </row>
-    <row r="177" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>359</v>
       </c>
@@ -22434,7 +22439,7 @@
       <c r="AL177" s="1"/>
       <c r="AM177" s="1"/>
     </row>
-    <row r="178" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>361</v>
       </c>
@@ -22648,7 +22653,7 @@
       <c r="AL179" s="1"/>
       <c r="AM179" s="1"/>
     </row>
-    <row r="180" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>364</v>
       </c>
@@ -22757,7 +22762,7 @@
       <c r="AL180" s="1"/>
       <c r="AM180" s="1"/>
     </row>
-    <row r="181" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>366</v>
       </c>
@@ -22866,7 +22871,7 @@
       <c r="AL181" s="1"/>
       <c r="AM181" s="1"/>
     </row>
-    <row r="182" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>368</v>
       </c>
@@ -22975,7 +22980,7 @@
       <c r="AL182" s="1"/>
       <c r="AM182" s="1"/>
     </row>
-    <row r="183" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>370</v>
       </c>
@@ -23084,7 +23089,7 @@
       <c r="AL183" s="1"/>
       <c r="AM183" s="1"/>
     </row>
-    <row r="184" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>372</v>
       </c>
@@ -23193,7 +23198,7 @@
       <c r="AL184" s="1"/>
       <c r="AM184" s="1"/>
     </row>
-    <row r="185" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>373</v>
       </c>
@@ -23302,7 +23307,7 @@
       <c r="AL185" s="1"/>
       <c r="AM185" s="1"/>
     </row>
-    <row r="186" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>374</v>
       </c>
@@ -23411,7 +23416,7 @@
       <c r="AL186" s="1"/>
       <c r="AM186" s="1"/>
     </row>
-    <row r="187" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>375</v>
       </c>
@@ -23520,7 +23525,7 @@
       <c r="AL187" s="1"/>
       <c r="AM187" s="1"/>
     </row>
-    <row r="188" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>376</v>
       </c>
@@ -23627,7 +23632,7 @@
       <c r="AL188" s="1"/>
       <c r="AM188" s="1"/>
     </row>
-    <row r="189" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>378</v>
       </c>
@@ -23736,7 +23741,7 @@
       <c r="AL189" s="1"/>
       <c r="AM189" s="1"/>
     </row>
-    <row r="190" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>380</v>
       </c>
@@ -23845,7 +23850,7 @@
       <c r="AL190" s="1"/>
       <c r="AM190" s="1"/>
     </row>
-    <row r="191" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>382</v>
       </c>
@@ -23954,7 +23959,7 @@
       <c r="AL191" s="1"/>
       <c r="AM191" s="1"/>
     </row>
-    <row r="192" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>383</v>
       </c>
@@ -24065,7 +24070,7 @@
       <c r="AL192" s="1"/>
       <c r="AM192" s="1"/>
     </row>
-    <row r="193" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>384</v>
       </c>
@@ -24178,7 +24183,7 @@
       <c r="AL193" s="1"/>
       <c r="AM193" s="1"/>
     </row>
-    <row r="194" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>387</v>
       </c>
@@ -24291,7 +24296,7 @@
       <c r="AL194" s="1"/>
       <c r="AM194" s="1"/>
     </row>
-    <row r="195" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>390</v>
       </c>
@@ -24402,7 +24407,7 @@
       <c r="AL195" s="1"/>
       <c r="AM195" s="1"/>
     </row>
-    <row r="196" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>391</v>
       </c>
@@ -24501,7 +24506,7 @@
       <c r="AL196" s="1"/>
       <c r="AM196" s="1"/>
     </row>
-    <row r="197" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>394</v>
       </c>
@@ -24610,7 +24615,7 @@
       <c r="AL197" s="1"/>
       <c r="AM197" s="1"/>
     </row>
-    <row r="198" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>396</v>
       </c>
@@ -24719,7 +24724,7 @@
       <c r="AL198" s="1"/>
       <c r="AM198" s="1"/>
     </row>
-    <row r="199" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>398</v>
       </c>
@@ -24828,7 +24833,7 @@
       <c r="AL199" s="1"/>
       <c r="AM199" s="1"/>
     </row>
-    <row r="200" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>399</v>
       </c>
@@ -24937,7 +24942,7 @@
       <c r="AL200" s="1"/>
       <c r="AM200" s="1"/>
     </row>
-    <row r="201" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>400</v>
       </c>
@@ -25046,7 +25051,7 @@
       <c r="AL201" s="1"/>
       <c r="AM201" s="1"/>
     </row>
-    <row r="202" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>401</v>
       </c>
@@ -25155,7 +25160,7 @@
       <c r="AL202" s="1"/>
       <c r="AM202" s="1"/>
     </row>
-    <row r="203" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>403</v>
       </c>
@@ -25264,7 +25269,7 @@
       <c r="AL203" s="1"/>
       <c r="AM203" s="1"/>
     </row>
-    <row r="204" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>404</v>
       </c>
@@ -25375,7 +25380,7 @@
       <c r="AL204" s="1"/>
       <c r="AM204" s="1"/>
     </row>
-    <row r="205" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>406</v>
       </c>
@@ -25476,7 +25481,7 @@
       <c r="AL205" s="1"/>
       <c r="AM205" s="1"/>
     </row>
-    <row r="206" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>410</v>
       </c>
@@ -25577,7 +25582,7 @@
       <c r="AL206" s="1"/>
       <c r="AM206" s="1"/>
     </row>
-    <row r="207" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>411</v>
       </c>
@@ -25678,7 +25683,7 @@
       <c r="AL207" s="1"/>
       <c r="AM207" s="1"/>
     </row>
-    <row r="208" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>412</v>
       </c>
@@ -25787,7 +25792,7 @@
       <c r="AL208" s="1"/>
       <c r="AM208" s="1"/>
     </row>
-    <row r="209" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>414</v>
       </c>
@@ -25898,7 +25903,7 @@
       <c r="AL209" s="1"/>
       <c r="AM209" s="1"/>
     </row>
-    <row r="210" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>415</v>
       </c>
@@ -26005,7 +26010,7 @@
       <c r="AL210" s="1"/>
       <c r="AM210" s="1"/>
     </row>
-    <row r="211" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>417</v>
       </c>
@@ -26114,7 +26119,7 @@
       <c r="AL211" s="1"/>
       <c r="AM211" s="1"/>
     </row>
-    <row r="212" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>419</v>
       </c>
@@ -26223,7 +26228,7 @@
       <c r="AL212" s="1"/>
       <c r="AM212" s="1"/>
     </row>
-    <row r="213" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>420</v>
       </c>
@@ -26332,7 +26337,7 @@
       <c r="AL213" s="1"/>
       <c r="AM213" s="1"/>
     </row>
-    <row r="214" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>421</v>
       </c>
@@ -26441,7 +26446,7 @@
       <c r="AL214" s="1"/>
       <c r="AM214" s="1"/>
     </row>
-    <row r="215" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>422</v>
       </c>
@@ -26550,7 +26555,7 @@
       <c r="AL215" s="1"/>
       <c r="AM215" s="1"/>
     </row>
-    <row r="216" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>424</v>
       </c>
@@ -26659,7 +26664,7 @@
       <c r="AL216" s="1"/>
       <c r="AM216" s="1"/>
     </row>
-    <row r="217" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>425</v>
       </c>
@@ -26768,7 +26773,7 @@
       <c r="AL217" s="1"/>
       <c r="AM217" s="1"/>
     </row>
-    <row r="218" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>426</v>
       </c>
@@ -26877,7 +26882,7 @@
       <c r="AL218" s="1"/>
       <c r="AM218" s="1"/>
     </row>
-    <row r="219" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>427</v>
       </c>
@@ -26986,7 +26991,7 @@
       <c r="AL219" s="1"/>
       <c r="AM219" s="1"/>
     </row>
-    <row r="220" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>428</v>
       </c>
@@ -27093,7 +27098,7 @@
       <c r="AL220" s="1"/>
       <c r="AM220" s="1"/>
     </row>
-    <row r="221" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>430</v>
       </c>
@@ -27200,7 +27205,7 @@
       <c r="AL221" s="1"/>
       <c r="AM221" s="1"/>
     </row>
-    <row r="222" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>432</v>
       </c>
@@ -27309,7 +27314,7 @@
       <c r="AL222" s="1"/>
       <c r="AM222" s="1"/>
     </row>
-    <row r="223" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>434</v>
       </c>
@@ -27418,7 +27423,7 @@
       <c r="AL223" s="1"/>
       <c r="AM223" s="1"/>
     </row>
-    <row r="224" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>436</v>
       </c>
@@ -27527,7 +27532,7 @@
       <c r="AL224" s="1"/>
       <c r="AM224" s="1"/>
     </row>
-    <row r="225" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>437</v>
       </c>
@@ -27636,7 +27641,7 @@
       <c r="AL225" s="1"/>
       <c r="AM225" s="1"/>
     </row>
-    <row r="226" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>438</v>
       </c>
@@ -27743,7 +27748,7 @@
       <c r="AL226" s="1"/>
       <c r="AM226" s="1"/>
     </row>
-    <row r="227" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>440</v>
       </c>
@@ -27850,7 +27855,7 @@
       <c r="AL227" s="1"/>
       <c r="AM227" s="1"/>
     </row>
-    <row r="228" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>441</v>
       </c>
@@ -27959,7 +27964,7 @@
       <c r="AL228" s="1"/>
       <c r="AM228" s="1"/>
     </row>
-    <row r="229" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>443</v>
       </c>
@@ -28066,7 +28071,7 @@
       <c r="AL229" s="1"/>
       <c r="AM229" s="1"/>
     </row>
-    <row r="230" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>445</v>
       </c>
@@ -28175,7 +28180,7 @@
       <c r="AL230" s="1"/>
       <c r="AM230" s="1"/>
     </row>
-    <row r="231" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>447</v>
       </c>
@@ -28284,7 +28289,7 @@
       <c r="AL231" s="1"/>
       <c r="AM231" s="1"/>
     </row>
-    <row r="232" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>448</v>
       </c>
@@ -28393,7 +28398,7 @@
       <c r="AL232" s="1"/>
       <c r="AM232" s="1"/>
     </row>
-    <row r="233" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>450</v>
       </c>
@@ -28502,7 +28507,7 @@
       <c r="AL233" s="1"/>
       <c r="AM233" s="1"/>
     </row>
-    <row r="234" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>451</v>
       </c>
@@ -28613,7 +28618,7 @@
       <c r="AL234" s="1"/>
       <c r="AM234" s="1"/>
     </row>
-    <row r="235" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>453</v>
       </c>
@@ -28724,7 +28729,7 @@
       <c r="AL235" s="1"/>
       <c r="AM235" s="1"/>
     </row>
-    <row r="236" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>455</v>
       </c>
@@ -28833,7 +28838,7 @@
       <c r="AL236" s="1"/>
       <c r="AM236" s="1"/>
     </row>
-    <row r="237" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>457</v>
       </c>
@@ -28942,7 +28947,7 @@
       <c r="AL237" s="1"/>
       <c r="AM237" s="1"/>
     </row>
-    <row r="238" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>458</v>
       </c>
@@ -29053,7 +29058,7 @@
       <c r="AL238" s="1"/>
       <c r="AM238" s="1"/>
     </row>
-    <row r="239" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>460</v>
       </c>
@@ -29162,7 +29167,7 @@
       <c r="AL239" s="1"/>
       <c r="AM239" s="1"/>
     </row>
-    <row r="240" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>462</v>
       </c>
@@ -29269,7 +29274,7 @@
       <c r="AL240" s="1"/>
       <c r="AM240" s="1"/>
     </row>
-    <row r="241" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>464</v>
       </c>
@@ -29376,7 +29381,7 @@
       <c r="AL241" s="1"/>
       <c r="AM241" s="1"/>
     </row>
-    <row r="242" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>465</v>
       </c>
@@ -29483,7 +29488,7 @@
       <c r="AL242" s="1"/>
       <c r="AM242" s="1"/>
     </row>
-    <row r="243" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>466</v>
       </c>
@@ -29590,7 +29595,7 @@
       <c r="AL243" s="1"/>
       <c r="AM243" s="1"/>
     </row>
-    <row r="244" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>467</v>
       </c>
@@ -29697,7 +29702,7 @@
       <c r="AL244" s="1"/>
       <c r="AM244" s="1"/>
     </row>
-    <row r="245" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>468</v>
       </c>
@@ -29806,7 +29811,7 @@
       <c r="AL245" s="1"/>
       <c r="AM245" s="1"/>
     </row>
-    <row r="246" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>470</v>
       </c>
@@ -29915,7 +29920,7 @@
       <c r="AL246" s="1"/>
       <c r="AM246" s="1"/>
     </row>
-    <row r="247" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>471</v>
       </c>
@@ -30026,7 +30031,7 @@
       <c r="AL247" s="1"/>
       <c r="AM247" s="1"/>
     </row>
-    <row r="248" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>474</v>
       </c>
@@ -30137,7 +30142,7 @@
       <c r="AL248" s="1"/>
       <c r="AM248" s="1"/>
     </row>
-    <row r="249" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>475</v>
       </c>
@@ -30246,7 +30251,7 @@
       <c r="AL249" s="1"/>
       <c r="AM249" s="1"/>
     </row>
-    <row r="250" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>476</v>
       </c>
@@ -30355,7 +30360,7 @@
       <c r="AL250" s="1"/>
       <c r="AM250" s="1"/>
     </row>
-    <row r="251" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>477</v>
       </c>
@@ -30464,7 +30469,7 @@
       <c r="AL251" s="1"/>
       <c r="AM251" s="1"/>
     </row>
-    <row r="252" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>478</v>
       </c>
@@ -30573,7 +30578,7 @@
       <c r="AL252" s="1"/>
       <c r="AM252" s="1"/>
     </row>
-    <row r="253" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>479</v>
       </c>
@@ -30682,7 +30687,7 @@
       <c r="AL253" s="1"/>
       <c r="AM253" s="1"/>
     </row>
-    <row r="254" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>480</v>
       </c>
@@ -30791,7 +30796,7 @@
       <c r="AL254" s="1"/>
       <c r="AM254" s="1"/>
     </row>
-    <row r="255" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>481</v>
       </c>
@@ -30900,7 +30905,7 @@
       <c r="AL255" s="1"/>
       <c r="AM255" s="1"/>
     </row>
-    <row r="256" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>482</v>
       </c>
@@ -31011,7 +31016,7 @@
       <c r="AL256" s="1"/>
       <c r="AM256" s="1"/>
     </row>
-    <row r="257" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>483</v>
       </c>
@@ -31120,7 +31125,7 @@
       <c r="AL257" s="1"/>
       <c r="AM257" s="1"/>
     </row>
-    <row r="258" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>485</v>
       </c>
@@ -31229,7 +31234,7 @@
       <c r="AL258" s="1"/>
       <c r="AM258" s="1"/>
     </row>
-    <row r="259" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>486</v>
       </c>
@@ -31338,7 +31343,7 @@
       <c r="AL259" s="1"/>
       <c r="AM259" s="1"/>
     </row>
-    <row r="260" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>487</v>
       </c>
@@ -31447,7 +31452,7 @@
       <c r="AL260" s="1"/>
       <c r="AM260" s="1"/>
     </row>
-    <row r="261" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>488</v>
       </c>
@@ -31556,7 +31561,7 @@
       <c r="AL261" s="1"/>
       <c r="AM261" s="1"/>
     </row>
-    <row r="262" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>489</v>
       </c>
@@ -31665,7 +31670,7 @@
       <c r="AL262" s="1"/>
       <c r="AM262" s="1"/>
     </row>
-    <row r="263" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>490</v>
       </c>
@@ -31774,7 +31779,7 @@
       <c r="AL263" s="1"/>
       <c r="AM263" s="1"/>
     </row>
-    <row r="264" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>491</v>
       </c>
@@ -31885,7 +31890,7 @@
       <c r="AL264" s="1"/>
       <c r="AM264" s="1"/>
     </row>
-    <row r="265" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>494</v>
       </c>
@@ -31994,7 +31999,7 @@
       <c r="AL265" s="1"/>
       <c r="AM265" s="1"/>
     </row>
-    <row r="266" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>495</v>
       </c>
@@ -32105,7 +32110,7 @@
       <c r="AL266" s="1"/>
       <c r="AM266" s="1"/>
     </row>
-    <row r="267" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>496</v>
       </c>
@@ -32216,7 +32221,7 @@
       <c r="AL267" s="1"/>
       <c r="AM267" s="1"/>
     </row>
-    <row r="268" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>497</v>
       </c>
@@ -32327,7 +32332,7 @@
       <c r="AL268" s="1"/>
       <c r="AM268" s="1"/>
     </row>
-    <row r="269" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>498</v>
       </c>
@@ -32438,7 +32443,7 @@
       <c r="AL269" s="1"/>
       <c r="AM269" s="1"/>
     </row>
-    <row r="270" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>499</v>
       </c>
@@ -32537,7 +32542,7 @@
       <c r="AL270" s="1"/>
       <c r="AM270" s="1"/>
     </row>
-    <row r="271" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>502</v>
       </c>
@@ -32636,7 +32641,7 @@
       <c r="AL271" s="1"/>
       <c r="AM271" s="1"/>
     </row>
-    <row r="272" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>504</v>
       </c>
@@ -32735,7 +32740,7 @@
       <c r="AL272" s="1"/>
       <c r="AM272" s="1"/>
     </row>
-    <row r="273" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>505</v>
       </c>
@@ -32842,7 +32847,7 @@
       <c r="AL273" s="1"/>
       <c r="AM273" s="1"/>
     </row>
-    <row r="274" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>507</v>
       </c>
@@ -32951,7 +32956,7 @@
       <c r="AL274" s="1"/>
       <c r="AM274" s="1"/>
     </row>
-    <row r="275" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>509</v>
       </c>
@@ -33060,7 +33065,7 @@
       <c r="AL275" s="1"/>
       <c r="AM275" s="1"/>
     </row>
-    <row r="276" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>510</v>
       </c>
@@ -33169,7 +33174,7 @@
       <c r="AL276" s="1"/>
       <c r="AM276" s="1"/>
     </row>
-    <row r="277" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>512</v>
       </c>
@@ -33278,7 +33283,7 @@
       <c r="AL277" s="1"/>
       <c r="AM277" s="1"/>
     </row>
-    <row r="278" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>514</v>
       </c>
@@ -33389,7 +33394,7 @@
       <c r="AL278" s="1"/>
       <c r="AM278" s="1"/>
     </row>
-    <row r="279" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>516</v>
       </c>
@@ -33498,7 +33503,7 @@
       <c r="AL279" s="1"/>
       <c r="AM279" s="1"/>
     </row>
-    <row r="280" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>518</v>
       </c>
@@ -33607,7 +33612,7 @@
       <c r="AL280" s="1"/>
       <c r="AM280" s="1"/>
     </row>
-    <row r="281" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>519</v>
       </c>
@@ -33716,7 +33721,7 @@
       <c r="AL281" s="1"/>
       <c r="AM281" s="1"/>
     </row>
-    <row r="282" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>521</v>
       </c>
@@ -33823,7 +33828,7 @@
       <c r="AL282" s="1"/>
       <c r="AM282" s="1"/>
     </row>
-    <row r="283" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>523</v>
       </c>
@@ -33932,7 +33937,7 @@
       <c r="AL283" s="1"/>
       <c r="AM283" s="1"/>
     </row>
-    <row r="284" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>524</v>
       </c>
@@ -34041,7 +34046,7 @@
       <c r="AL284" s="1"/>
       <c r="AM284" s="1"/>
     </row>
-    <row r="285" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>525</v>
       </c>
@@ -34150,7 +34155,7 @@
       <c r="AL285" s="1"/>
       <c r="AM285" s="1"/>
     </row>
-    <row r="286" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>526</v>
       </c>
@@ -34259,7 +34264,7 @@
       <c r="AL286" s="1"/>
       <c r="AM286" s="1"/>
     </row>
-    <row r="287" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>528</v>
       </c>
@@ -34368,7 +34373,7 @@
       <c r="AL287" s="1"/>
       <c r="AM287" s="1"/>
     </row>
-    <row r="288" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>530</v>
       </c>
@@ -34477,7 +34482,7 @@
       <c r="AL288" s="1"/>
       <c r="AM288" s="1"/>
     </row>
-    <row r="289" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>532</v>
       </c>
@@ -34586,7 +34591,7 @@
       <c r="AL289" s="1"/>
       <c r="AM289" s="1"/>
     </row>
-    <row r="290" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>533</v>
       </c>
@@ -34695,7 +34700,7 @@
       <c r="AL290" s="1"/>
       <c r="AM290" s="1"/>
     </row>
-    <row r="291" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>534</v>
       </c>
@@ -34806,7 +34811,7 @@
       <c r="AL291" s="1"/>
       <c r="AM291" s="1"/>
     </row>
-    <row r="292" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>536</v>
       </c>
@@ -34919,7 +34924,7 @@
       <c r="AL292" s="1"/>
       <c r="AM292" s="1"/>
     </row>
-    <row r="293" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>539</v>
       </c>
@@ -35030,7 +35035,7 @@
       <c r="AL293" s="1"/>
       <c r="AM293" s="1"/>
     </row>
-    <row r="294" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>542</v>
       </c>
@@ -35139,7 +35144,7 @@
       <c r="AL294" s="1"/>
       <c r="AM294" s="1"/>
     </row>
-    <row r="295" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>543</v>
       </c>
@@ -35250,7 +35255,7 @@
       <c r="AL295" s="1"/>
       <c r="AM295" s="1"/>
     </row>
-    <row r="296" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>545</v>
       </c>
@@ -35361,7 +35366,7 @@
       <c r="AL296" s="1"/>
       <c r="AM296" s="1"/>
     </row>
-    <row r="297" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>547</v>
       </c>
@@ -35470,7 +35475,7 @@
       <c r="AL297" s="1"/>
       <c r="AM297" s="1"/>
     </row>
-    <row r="298" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>549</v>
       </c>
@@ -35581,7 +35586,7 @@
       <c r="AL298" s="1"/>
       <c r="AM298" s="1"/>
     </row>
-    <row r="299" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>551</v>
       </c>
@@ -35692,7 +35697,7 @@
       <c r="AL299" s="1"/>
       <c r="AM299" s="1"/>
     </row>
-    <row r="300" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>552</v>
       </c>
@@ -35803,7 +35808,7 @@
       <c r="AL300" s="1"/>
       <c r="AM300" s="1"/>
     </row>
-    <row r="301" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>553</v>
       </c>
@@ -35914,7 +35919,7 @@
       <c r="AL301" s="1"/>
       <c r="AM301" s="1"/>
     </row>
-    <row r="302" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>554</v>
       </c>
@@ -36021,7 +36026,7 @@
       <c r="AL302" s="1"/>
       <c r="AM302" s="1"/>
     </row>
-    <row r="303" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>556</v>
       </c>
@@ -36128,7 +36133,7 @@
       <c r="AL303" s="1"/>
       <c r="AM303" s="1"/>
     </row>
-    <row r="304" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>557</v>
       </c>
@@ -36235,7 +36240,7 @@
       <c r="AL304" s="1"/>
       <c r="AM304" s="1"/>
     </row>
-    <row r="305" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>558</v>
       </c>
@@ -36342,7 +36347,7 @@
       <c r="AL305" s="1"/>
       <c r="AM305" s="1"/>
     </row>
-    <row r="306" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>560</v>
       </c>
@@ -36449,7 +36454,7 @@
       <c r="AL306" s="1"/>
       <c r="AM306" s="1"/>
     </row>
-    <row r="307" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>562</v>
       </c>
@@ -36556,7 +36561,7 @@
       <c r="AL307" s="1"/>
       <c r="AM307" s="1"/>
     </row>
-    <row r="308" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>564</v>
       </c>
@@ -36663,7 +36668,7 @@
       <c r="AL308" s="1"/>
       <c r="AM308" s="1"/>
     </row>
-    <row r="309" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>566</v>
       </c>
@@ -36772,7 +36777,7 @@
       <c r="AL309" s="1"/>
       <c r="AM309" s="1"/>
     </row>
-    <row r="310" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>568</v>
       </c>
@@ -36871,7 +36876,7 @@
       <c r="AM310" s="1"/>
       <c r="AN310" s="1"/>
     </row>
-    <row r="311" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>571</v>
       </c>
@@ -36979,7 +36984,7 @@
       <c r="AL311" s="1"/>
       <c r="AM311" s="1"/>
     </row>
-    <row r="312" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>573</v>
       </c>
@@ -37088,7 +37093,7 @@
       <c r="AL312" s="1"/>
       <c r="AM312" s="1"/>
     </row>
-    <row r="313" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>575</v>
       </c>
@@ -37197,7 +37202,7 @@
       <c r="AL313" s="1"/>
       <c r="AM313" s="1"/>
     </row>
-    <row r="314" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>576</v>
       </c>
@@ -37306,7 +37311,7 @@
       <c r="AL314" s="1"/>
       <c r="AM314" s="1"/>
     </row>
-    <row r="315" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>577</v>
       </c>
@@ -37415,7 +37420,7 @@
       <c r="AL315" s="1"/>
       <c r="AM315" s="1"/>
     </row>
-    <row r="316" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>579</v>
       </c>
@@ -37524,7 +37529,7 @@
       <c r="AL316" s="1"/>
       <c r="AM316" s="1"/>
     </row>
-    <row r="317" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>580</v>
       </c>
@@ -37633,7 +37638,7 @@
       <c r="AL317" s="1"/>
       <c r="AM317" s="1"/>
     </row>
-    <row r="318" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>581</v>
       </c>
@@ -37742,7 +37747,7 @@
       <c r="AL318" s="1"/>
       <c r="AM318" s="1"/>
     </row>
-    <row r="319" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>583</v>
       </c>
@@ -37853,7 +37858,7 @@
       <c r="AL319" s="1"/>
       <c r="AM319" s="1"/>
     </row>
-    <row r="320" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:40" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>585</v>
       </c>
@@ -37960,7 +37965,7 @@
       <c r="AL320" s="1"/>
       <c r="AM320" s="1"/>
     </row>
-    <row r="321" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>587</v>
       </c>
@@ -38067,7 +38072,7 @@
       <c r="AL321" s="1"/>
       <c r="AM321" s="1"/>
     </row>
-    <row r="322" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>589</v>
       </c>
@@ -38176,7 +38181,7 @@
       <c r="AL322" s="1"/>
       <c r="AM322" s="1"/>
     </row>
-    <row r="323" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>591</v>
       </c>
@@ -38283,7 +38288,7 @@
       <c r="AL323" s="1"/>
       <c r="AM323" s="1"/>
     </row>
-    <row r="324" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>593</v>
       </c>
@@ -38390,7 +38395,7 @@
       <c r="AL324" s="1"/>
       <c r="AM324" s="1"/>
     </row>
-    <row r="325" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>595</v>
       </c>
@@ -38499,7 +38504,7 @@
       <c r="AL325" s="1"/>
       <c r="AM325" s="1"/>
     </row>
-    <row r="326" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>597</v>
       </c>
@@ -38596,7 +38601,7 @@
       <c r="AL326" s="1"/>
       <c r="AM326" s="1"/>
     </row>
-    <row r="327" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>600</v>
       </c>
@@ -38695,7 +38700,7 @@
       <c r="AL327" s="1"/>
       <c r="AM327" s="1"/>
     </row>
-    <row r="328" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>604</v>
       </c>
@@ -38802,7 +38807,7 @@
       <c r="AL328" s="1"/>
       <c r="AM328" s="1"/>
     </row>
-    <row r="329" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>605</v>
       </c>
@@ -38909,7 +38914,7 @@
       <c r="AL329" s="1"/>
       <c r="AM329" s="1"/>
     </row>
-    <row r="330" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>606</v>
       </c>
@@ -39018,7 +39023,7 @@
       <c r="AL330" s="1"/>
       <c r="AM330" s="1"/>
     </row>
-    <row r="331" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>607</v>
       </c>
@@ -39117,7 +39122,7 @@
       <c r="AL331" s="1"/>
       <c r="AM331" s="1"/>
     </row>
-    <row r="332" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>609</v>
       </c>
@@ -39226,7 +39231,7 @@
       <c r="AL332" s="1"/>
       <c r="AM332" s="1"/>
     </row>
-    <row r="333" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>611</v>
       </c>
@@ -39325,7 +39330,7 @@
       <c r="AL333" s="1"/>
       <c r="AM333" s="1"/>
     </row>
-    <row r="334" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>613</v>
       </c>
@@ -39424,7 +39429,7 @@
       <c r="AL334" s="1"/>
       <c r="AM334" s="1"/>
     </row>
-    <row r="335" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>614</v>
       </c>
@@ -39535,7 +39540,7 @@
       <c r="AL335" s="1"/>
       <c r="AM335" s="1"/>
     </row>
-    <row r="336" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>616</v>
       </c>
@@ -39644,7 +39649,7 @@
       <c r="AL336" s="1"/>
       <c r="AM336" s="1"/>
     </row>
-    <row r="337" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>617</v>
       </c>
@@ -39755,7 +39760,7 @@
       <c r="AL337" s="1"/>
       <c r="AM337" s="1"/>
     </row>
-    <row r="338" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>619</v>
       </c>
@@ -39866,7 +39871,7 @@
       <c r="AL338" s="1"/>
       <c r="AM338" s="1"/>
     </row>
-    <row r="339" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>620</v>
       </c>
@@ -39965,7 +39970,7 @@
       <c r="AL339" s="1"/>
       <c r="AM339" s="1"/>
     </row>
-    <row r="340" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>621</v>
       </c>
@@ -40064,7 +40069,7 @@
       <c r="AL340" s="1"/>
       <c r="AM340" s="1"/>
     </row>
-    <row r="341" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>622</v>
       </c>
@@ -40163,7 +40168,7 @@
       <c r="AL341" s="1"/>
       <c r="AM341" s="1"/>
     </row>
-    <row r="342" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>623</v>
       </c>
@@ -40262,7 +40267,7 @@
       <c r="AL342" s="1"/>
       <c r="AM342" s="1"/>
     </row>
-    <row r="343" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>625</v>
       </c>
@@ -40369,7 +40374,7 @@
       <c r="AL343" s="1"/>
       <c r="AM343" s="1"/>
     </row>
-    <row r="344" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>628</v>
       </c>
@@ -40476,7 +40481,7 @@
       <c r="AL344" s="1"/>
       <c r="AM344" s="1"/>
     </row>
-    <row r="345" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>629</v>
       </c>
@@ -40587,7 +40592,7 @@
       <c r="AL345" s="1"/>
       <c r="AM345" s="1"/>
     </row>
-    <row r="346" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>631</v>
       </c>
@@ -40698,7 +40703,7 @@
       <c r="AL346" s="1"/>
       <c r="AM346" s="1"/>
     </row>
-    <row r="347" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>633</v>
       </c>
@@ -40809,7 +40814,7 @@
       <c r="AL347" s="1"/>
       <c r="AM347" s="1"/>
     </row>
-    <row r="348" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>636</v>
       </c>
@@ -40918,7 +40923,7 @@
       <c r="AL348" s="1"/>
       <c r="AM348" s="1"/>
     </row>
-    <row r="349" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>638</v>
       </c>
@@ -41029,7 +41034,7 @@
       <c r="AL349" s="1"/>
       <c r="AM349" s="1"/>
     </row>
-    <row r="350" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>640</v>
       </c>
@@ -41140,7 +41145,7 @@
       <c r="AL350" s="1"/>
       <c r="AM350" s="1"/>
     </row>
-    <row r="351" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>641</v>
       </c>
@@ -41251,7 +41256,7 @@
       <c r="AL351" s="1"/>
       <c r="AM351" s="1"/>
     </row>
-    <row r="352" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>642</v>
       </c>
@@ -41362,7 +41367,7 @@
       <c r="AL352" s="1"/>
       <c r="AM352" s="1"/>
     </row>
-    <row r="353" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>643</v>
       </c>
@@ -41469,7 +41474,7 @@
       <c r="AL353" s="1"/>
       <c r="AM353" s="1"/>
     </row>
-    <row r="354" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>645</v>
       </c>
@@ -41580,7 +41585,7 @@
       <c r="AL354" s="1"/>
       <c r="AM354" s="1"/>
     </row>
-    <row r="355" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>648</v>
       </c>
@@ -41691,7 +41696,7 @@
       <c r="AL355" s="1"/>
       <c r="AM355" s="1"/>
     </row>
-    <row r="356" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>649</v>
       </c>
@@ -41800,7 +41805,7 @@
       <c r="AL356" s="1"/>
       <c r="AM356" s="1"/>
     </row>
-    <row r="357" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>650</v>
       </c>
@@ -41911,7 +41916,7 @@
       <c r="AL357" s="1"/>
       <c r="AM357" s="1"/>
     </row>
-    <row r="358" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>651</v>
       </c>
@@ -42020,7 +42025,7 @@
       <c r="AL358" s="1"/>
       <c r="AM358" s="1"/>
     </row>
-    <row r="359" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>653</v>
       </c>
@@ -42129,7 +42134,7 @@
       <c r="AL359" s="1"/>
       <c r="AM359" s="1"/>
     </row>
-    <row r="360" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>654</v>
       </c>
@@ -42238,7 +42243,7 @@
       <c r="AL360" s="1"/>
       <c r="AM360" s="1"/>
     </row>
-    <row r="361" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:39" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>655</v>
       </c>
@@ -42635,7 +42640,13 @@
       <c r="AM368" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AI361" xr:uid="{BF10B127-6165-4A57-AAED-596F28B83BE3}"/>
+  <autoFilter ref="B1:AI361" xr:uid="{BF10B127-6165-4A57-AAED-596F28B83BE3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Leche en polvo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>